--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O15" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1834,68 +1834,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1993,68 +1993,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1834,68 +1834,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1993,68 +1993,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P15" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2666,10 +2666,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3143,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P5" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P14" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O15" t="n">
-        <v>4.8</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,27 +678,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46223.53125</v>
+        <v>46223.52083333334</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46223.54166666666</v>
+        <v>46223.53125</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46223.58333333334</v>
+        <v>46223.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.89</v>
+        <v>4.24</v>
       </c>
       <c r="O5" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46223.58333333334</v>
+        <v>46223.55208333334</v>
       </c>
     </row>
     <row r="6">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46223.58333333334</v>
+        <v>46223.5625</v>
       </c>
     </row>
     <row r="7">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,16 +1553,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46223.625</v>
+        <v>46223.58333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.94</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,10 +1712,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46223.625</v>
+        <v>46223.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1834,68 +1834,68 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.55</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46223.66666666666</v>
+        <v>46223.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46223.66666666666</v>
+        <v>46223.625</v>
       </c>
     </row>
     <row r="11">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46223.67708333334</v>
+        <v>46223.625</v>
       </c>
     </row>
     <row r="12">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46223.67708333334</v>
+        <v>46223.625</v>
       </c>
     </row>
     <row r="13">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.09</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46223.83333333334</v>
+        <v>46223.625</v>
       </c>
     </row>
     <row r="14">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46223.83333333334</v>
+        <v>46223.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2745,27 +2745,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.53</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>2.71</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2825,16 +2825,16 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46223.83333333334</v>
+        <v>46223.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.66666666666</v>
       </c>
     </row>
     <row r="17">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.67708333334</v>
       </c>
     </row>
     <row r="19">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3461,10 +3461,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.67708333334</v>
       </c>
     </row>
     <row r="20">
@@ -3540,156 +3540,792 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Patronato</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>46223.83333333334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>46223.83333333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n">
+        <v>46223.83333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Chaco For Ever</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" s="3" t="n">
+        <v>46223.875</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Argentina Prim B Nacional</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Central Norte</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Deportivo Morón</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N20" t="n">
+      <c r="N24" t="n">
         <v>2.78</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O24" t="n">
         <v>2.7</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P24" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.71</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z24" t="n">
         <v>2</v>
       </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" s="3" t="n">
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="3" t="n">
         <v>46223.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.25</v>
       </c>
-      <c r="U13" t="n">
-        <v>4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.89</v>
+        <v>4.09</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,10 +2507,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2348,10 +2348,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.48</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>4.09</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.25</v>
       </c>
-      <c r="U10" t="n">
-        <v>4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU24"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4097,16 +4097,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.83333333334</v>
       </c>
     </row>
     <row r="24">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,109 +4223,268 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>2.19</v>
       </c>
       <c r="O24" t="n">
         <v>2.7</v>
       </c>
       <c r="P24" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" s="3" t="n">
+        <v>46223.875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Deportivo Morón</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O25" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="P25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.71</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z25" t="n">
         <v>2</v>
       </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" s="3" t="n">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" s="3" t="n">
         <v>46223.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,10 +2189,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>2.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.89</v>
+        <v>4.09</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>4.09</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
         <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
         <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P10" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.25</v>
       </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,34 +734,34 @@
         <v>3.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
@@ -770,19 +770,19 @@
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,16 +1052,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,34 +1211,34 @@
         <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.92</v>
@@ -1247,19 +1247,19 @@
         <v>1.76</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,55 +1370,55 @@
         <v>5.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,34 +1529,34 @@
         <v>4.48</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA7" t="n">
         <v>1.85</v>
@@ -1565,19 +1565,19 @@
         <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O10" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U11" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R12" t="n">
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.3</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,55 +3278,55 @@
         <v>2.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3437,40 +3437,40 @@
         <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AC19" t="n">
         <v>1.77</v>
@@ -3479,13 +3479,13 @@
         <v>1.91</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O20" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.97</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
         <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>4.09</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4097,16 +4097,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>2</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU25"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,27 +678,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.29</v>
+        <v>8.85</v>
       </c>
       <c r="O2" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>3.14</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.97</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.73</v>
+        <v>2.23</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.35</v>
+        <v>2.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46223.52083333334</v>
+        <v>46223.5</v>
       </c>
     </row>
     <row r="3">
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
         <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.95</v>
+        <v>3.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46223.53125</v>
+        <v>46223.52083333334</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,25 +1043,25 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46223.54166666666</v>
+        <v>46223.53125</v>
       </c>
     </row>
     <row r="5">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46223.55208333334</v>
+        <v>46223.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.51</v>
+        <v>4.24</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P6" t="n">
-        <v>5.7</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>5.03</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB6" t="n">
         <v>1.76</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.57</v>
+        <v>2.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.41</v>
+        <v>1.09</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46223.5625</v>
+        <v>46223.55208333334</v>
       </c>
     </row>
     <row r="7">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>4.48</v>
+        <v>5.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="U7" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.72</v>
+        <v>2.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.85</v>
+        <v>2.41</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46223.58333333334</v>
+        <v>46223.5625</v>
       </c>
     </row>
     <row r="8">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>4.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.26</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.88</v>
+        <v>6.89</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="P10" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.71</v>
+        <v>6.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.89</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.09</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.73</v>
+        <v>1.08</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46223.625</v>
+        <v>46223.58333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG11" t="n">
         <v>1.5</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2586,27 +2586,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.31</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>2.96</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>3.01</v>
       </c>
       <c r="R14" t="n">
-        <v>2.33</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>3.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.63</v>
+        <v>6.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>2.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46223.64583333334</v>
+        <v>46223.625</v>
       </c>
     </row>
     <row r="15">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>4.4</v>
+        <v>5.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.25</v>
+        <v>3.28</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46223.66666666666</v>
+        <v>46223.64583333334</v>
       </c>
     </row>
     <row r="17">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,85 +3265,85 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.5</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
         <v>2.33</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46223.67708333334</v>
+        <v>46223.66666666666</v>
       </c>
     </row>
     <row r="19">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,81 +3587,81 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>4.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.3</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46223.83333333334</v>
+        <v>46223.67708333334</v>
       </c>
     </row>
     <row r="21">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
         <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>4.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.97</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.19</v>
+        <v>2.53</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>3.67</v>
+        <v>2.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
         <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46223.875</v>
+        <v>46223.83333333334</v>
       </c>
     </row>
     <row r="25">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.78</v>
+        <v>2.19</v>
       </c>
       <c r="O25" t="n">
         <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.7</v>
+        <v>3.67</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,10 +4415,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
         <v>3.4</v>
@@ -4485,6 +4485,165 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
+        <v>46223.875</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Deportivo Morón</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" s="3" t="n">
         <v>46223.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.17</v>
+        <v>6.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.58</v>
+        <v>5.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.1</v>
+        <v>3.17</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U11" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.89</v>
+        <v>6.85</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG11" t="n">
         <v>1.5</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
         <v>1.5</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3779,16 +3779,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="P22" t="n">
-        <v>4.09</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>2.97</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.35</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AB24" t="n">
         <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG11" t="n">
         <v>1.5</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="R14" t="n">
         <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.76</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="AB23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC23" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="O24" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
         <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,55 +734,55 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="n">
         <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1052,28 +1052,28 @@
         <v>4.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.24</v>
@@ -1211,55 +1211,55 @@
         <v>2.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.1</v>
+        <v>3.17</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="R9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.2</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.81</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.34</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
         <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC11" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AK11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3.26</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>6.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE12" t="n">
         <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>2.96</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.67</v>
+        <v>2.31</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>5.11</v>
+        <v>2.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,37 +3746,37 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
         <v>1.55</v>
@@ -3785,26 +3785,26 @@
         <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O22" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="T23" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.95</v>
+        <v>4.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB23" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.36</v>
+        <v>1.51</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.76</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="AB24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC24" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
         <v>1.5</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>3.46</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
         <v>1.22</v>
@@ -3143,10 +3143,10 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
         <v>1.31</v>
@@ -3158,16 +3158,16 @@
         <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
         <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,37 +3746,37 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.88</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>4.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>1.55</v>
@@ -3785,25 +3785,25 @@
         <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.41</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,37 +3905,37 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P22" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
         <v>1.55</v>
@@ -3944,26 +3944,26 @@
         <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>4.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>2.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.42</v>
+        <v>2.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.21</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.1</v>
+        <v>3.17</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>6.89</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P10" t="n">
-        <v>4.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="R10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.2</v>
       </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.81</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.84</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U12" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.75</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.89</v>
+        <v>6.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG12" t="n">
         <v>1.5</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.26</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.85</v>
+        <v>5.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,37 +3746,37 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.88</v>
+        <v>2.53</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>4.09</v>
+        <v>2.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
         <v>1.55</v>
@@ -3785,26 +3785,26 @@
         <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.76</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="AB22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC22" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.53</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="T24" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>4.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="AA24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB24" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.36</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -902,7 +902,7 @@
         <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
@@ -923,25 +923,25 @@
         <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
         <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.24</v>
+        <v>6.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.03</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
         <v>2.62</v>
@@ -1388,37 +1388,37 @@
         <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
         <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>6.89</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.17</v>
+        <v>6.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.58</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.89</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.1</v>
+        <v>3.17</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>4.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
         <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.01</v>
+        <v>2.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.85</v>
+        <v>5.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
         <v>1.5</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>4.4</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.71</v>
+        <v>3.22</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.26</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.95</v>
+        <v>6.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.11</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.31</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.3</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W16" t="n">
+      <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AF16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.23</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.53</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>4.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.76</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC21" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>2.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="T22" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.95</v>
+        <v>4.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="AA22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AB22" t="n">
-        <v>2.97</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.36</v>
+        <v>1.51</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="O24" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
         <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
         <v>1.33</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.4</v>
+        <v>6.41</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,25 +734,25 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.86</v>
+        <v>7.03</v>
       </c>
       <c r="R2" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -776,13 +776,13 @@
         <v>1.58</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O4" t="n">
         <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
         <v>2.3</v>
@@ -1064,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
@@ -1076,25 +1076,25 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
         <v>1.75</v>
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>1.36</v>
@@ -1223,43 +1223,43 @@
         <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
         <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T7" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1553,22 +1553,22 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
         <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.57</v>
+        <v>3.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
         <v>1.05</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>4.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>2.77</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.42</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,34 +1838,34 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
         <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1874,28 +1874,28 @@
         <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB9" t="n">
         <v>2.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>2.89</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.86</v>
+        <v>1.94</v>
       </c>
       <c r="O10" t="n">
         <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.29</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,22 +2156,22 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
         <v>2.05</v>
@@ -2180,28 +2180,28 @@
         <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
         <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>6.43</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
@@ -2210,10 +2210,10 @@
         <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,47 +2348,47 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>4.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.22</v>
+        <v>2.77</v>
       </c>
       <c r="R13" t="n">
         <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2510,28 +2510,28 @@
         <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2642,10 +2642,10 @@
         <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S14" t="n">
         <v>1.62</v>
@@ -2669,16 +2669,16 @@
         <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
         <v>1.04</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3311,7 +3311,7 @@
         <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
         <v>1.86</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.32</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.23</v>
+        <v>2.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
         <v>2.56</v>
@@ -3764,13 +3764,13 @@
         <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
         <v>1.23</v>
@@ -3785,10 +3785,10 @@
         <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AC21" t="n">
         <v>1.85</v>
@@ -3803,7 +3803,7 @@
         <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.62</v>
       </c>
-      <c r="P22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Q22" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S22" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
         <v>2.16</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>4.09</v>
+        <v>3.39</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,25 +4223,25 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
         <v>2.71</v>
       </c>
       <c r="P24" t="n">
-        <v>2.89</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
         <v>4</v>
@@ -4250,53 +4250,53 @@
         <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
         <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.41</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,19 +734,19 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.03</v>
+        <v>6.87</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="S2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
         <v>1.62</v>
@@ -767,22 +767,22 @@
         <v>1.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE2" t="n">
         <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
         <v>2.88</v>
@@ -1562,7 +1562,7 @@
         <v>2.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
         <v>3.34</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>2.89</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.89</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,80 +1997,80 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.24</v>
       </c>
-      <c r="Z10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.43</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,28 +2315,28 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>2.77</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="V12" t="n">
         <v>1.18</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.75</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U13" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.89</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2795,61 +2795,61 @@
         <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.07</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,77 +2954,77 @@
         <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.05</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T20" t="n">
         <v>4.1</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.5</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.85</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T21" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>2.88</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.92</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.83</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.39</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O24" t="n">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.89</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.54</v>
+        <v>4.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.64</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>2.89</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,61 +2315,61 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>4.75</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U12" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.89</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG12" t="n">
         <v>1.5</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>6.43</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
         <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>3.27</v>
+        <v>4.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.43</v>
+        <v>5.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2795,77 +2795,77 @@
         <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.91</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,61 +2954,61 @@
         <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.05</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.29</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.61</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.35</v>
       </c>
-      <c r="O22" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.83</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.18</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.39</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.94</v>
+        <v>6.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>1.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.2</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.04</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>2.89</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.9</v>
+        <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.6</v>
       </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.89</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.14</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.43</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>3.27</v>
+        <v>4.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.43</v>
+        <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.77</v>
+        <v>3.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
         <v>1.18</v>
@@ -2666,47 +2666,47 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.7</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T19" t="n">
         <v>4.1</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.5</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="W19" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>2.17</v>
       </c>
       <c r="O23" t="n">
-        <v>4.85</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>5.2</v>
+        <v>3.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.17</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>3.39</v>
+        <v>5.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,25 +734,25 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.87</v>
+        <v>6.93</v>
       </c>
       <c r="R2" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T2" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -779,10 +779,10 @@
         <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
         <v>1.02</v>
@@ -902,7 +902,7 @@
         <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,16 +1052,16 @@
         <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
         <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
         <v>2.6</v>
@@ -1070,10 +1070,10 @@
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
         <v>1.23</v>
@@ -1085,7 +1085,7 @@
         <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
         <v>2.97</v>
@@ -1097,10 +1097,10 @@
         <v>1.08</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
         <v>2.88</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.3</v>
+        <v>4.85</v>
       </c>
       <c r="O6" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
@@ -1382,34 +1382,34 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
         <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
@@ -1434,7 +1434,7 @@
         <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
         <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1553,13 +1553,13 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
         <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
         <v>1.76</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
@@ -1712,25 +1712,25 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
         <v>1.72</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>6.5</v>
@@ -1856,16 +1856,16 @@
         <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1874,7 +1874,7 @@
         <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA9" t="n">
         <v>1.48</v>
@@ -2003,7 +2003,7 @@
         <v>3.54</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Q10" t="n">
         <v>3.18</v>
@@ -2012,16 +2012,16 @@
         <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T10" t="n">
         <v>3.28</v>
       </c>
       <c r="U10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
         <v>1.08</v>
@@ -2033,28 +2033,28 @@
         <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE10" t="n">
         <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
         <v>3.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.43</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.81</v>
@@ -2336,7 +2336,7 @@
         <v>2.01</v>
       </c>
       <c r="U12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
@@ -2348,10 +2348,10 @@
         <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA12" t="n">
         <v>3.08</v>
@@ -2388,7 +2388,7 @@
         <v>1.16</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U13" t="n">
         <v>3.82</v>
@@ -2516,13 +2516,13 @@
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
         <v>1.7</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="U14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.61</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.05</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T20" t="n">
         <v>4.1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="U20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.87</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
         <v>1.38</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.81</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.88</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.39</v>
+        <v>2.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>2.81</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="P26" t="n">
         <v>2.5</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -941,7 +941,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1388,7 +1388,7 @@
         <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
@@ -1400,16 +1400,16 @@
         <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
@@ -1418,7 +1418,7 @@
         <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
         <v>1.07</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
         <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2477,13 +2477,13 @@
         <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.75</v>
@@ -2519,7 +2519,7 @@
         <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.89</v>
+        <v>5.87</v>
       </c>
       <c r="AD13" t="n">
         <v>1.09</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
         <v>3.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2846,7 +2846,7 @@
         <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
         <v>1.93</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
         <v>1.9</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.37</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="Q16" t="n">
         <v>2.3</v>
@@ -3002,13 +3002,13 @@
         <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
         <v>1.38</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
         <v>1.38</v>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
         <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4073,7 +4073,7 @@
         <v>2.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
         <v>1.83</v>
@@ -4106,7 +4106,7 @@
         <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC23" t="n">
         <v>5.65</v>
@@ -4137,7 +4137,7 @@
         <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4226,10 +4226,10 @@
         <v>2.3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
         <v>2.81</v>
@@ -4238,13 +4238,13 @@
         <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V24" t="n">
         <v>1.15</v>
@@ -4296,7 +4296,7 @@
         <v>1.44</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
         <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.01</v>
+        <v>3.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
         <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>3.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="U13" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
         <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="U14" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
         <v>1.18</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.05</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>3.76</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="O21" t="n">
-        <v>4.85</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.83</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.35</v>
+        <v>2.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.81</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
         <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U8" t="n">
         <v>2.4</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.18</v>
+        <v>2.55</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="O10" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.18</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
         <v>3.25</v>
@@ -2168,52 +2168,52 @@
         <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
         <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
         <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>4.33</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG14" t="n">
         <v>1.5</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.6</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.76</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.05</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.86</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.56</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
         <v>1.38</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
         <v>1.38</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P21" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.81</v>
+        <v>3.17</v>
       </c>
       <c r="R22" t="n">
         <v>1.92</v>
@@ -3923,7 +3923,7 @@
         <v>1.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
         <v>4.25</v>
@@ -3938,7 +3938,7 @@
         <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
         <v>2.11</v>
@@ -3953,10 +3953,10 @@
         <v>6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
         <v>2.38</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
         <v>1.51</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.35</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.91</v>
+        <v>5.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.83</v>
       </c>
-      <c r="S24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.35</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -743,7 +743,7 @@
         <v>1.24</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.25</v>
@@ -761,10 +761,10 @@
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB2" t="n">
         <v>2.4</v>
@@ -776,7 +776,7 @@
         <v>1.59</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
         <v>1.75</v>
@@ -899,10 +899,10 @@
         <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.76</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
@@ -920,7 +920,7 @@
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="n">
         <v>2.08</v>
@@ -941,7 +941,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1079,13 +1079,13 @@
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="n">
         <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC4" t="n">
         <v>2.97</v>
@@ -1094,7 +1094,7 @@
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
         <v>1.74</v>
@@ -1217,7 +1217,7 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
         <v>2.65</v>
@@ -1229,7 +1229,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1256,10 +1256,10 @@
         <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
         <v>1.48</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.85</v>
+        <v>6.75</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1391,25 +1391,25 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.42</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
         <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O7" t="n">
         <v>3.85</v>
@@ -1535,13 +1535,13 @@
         <v>2.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.35</v>
@@ -1553,13 +1553,13 @@
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB7" t="n">
         <v>1.76</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1682,25 +1682,25 @@
         <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="R8" t="n">
         <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
@@ -1709,25 +1709,25 @@
         <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
         <v>2.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
         <v>1.19</v>
@@ -1752,7 +1752,7 @@
         <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1856,13 +1856,13 @@
         <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
         <v>1.14</v>
@@ -1871,31 +1871,31 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="AA9" t="n">
         <v>1.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
         <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AK9" t="n">
         <v>1.11</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>3.03</v>
       </c>
       <c r="Q10" t="n">
         <v>2.4</v>
@@ -2036,13 +2036,13 @@
         <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="AD10" t="n">
         <v>1.3</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
         <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
         <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
         <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2351,44 +2351,44 @@
         <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,61 +2474,61 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U13" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AG13" t="n">
         <v>1.5</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
         <v>1.5</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3269,31 +3269,31 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="R18" t="n">
         <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
         <v>2.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
         <v>1.06</v>
@@ -3302,31 +3302,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
         <v>1.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF18" t="n">
         <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.13</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
         <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
         <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
         <v>1.83</v>
@@ -4100,13 +4100,13 @@
         <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AA23" t="n">
         <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
         <v>5.65</v>
@@ -4137,7 +4137,7 @@
         <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>3.17</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.31</v>
+        <v>2.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.92</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
         <v>2.68</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU26"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,13 +743,13 @@
         <v>1.24</v>
       </c>
       <c r="T2" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="U2" t="n">
         <v>2.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -761,28 +761,28 @@
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB2" t="n">
         <v>2.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD2" t="n">
         <v>1.59</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF2" t="n">
         <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
         <v>2.97</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
         <v>2.65</v>
@@ -1229,7 +1229,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -1241,25 +1241,25 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
         <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK5" t="n">
         <v>1.48</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
         <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="Q7" t="n">
         <v>2.08</v>
@@ -1541,10 +1541,10 @@
         <v>2.66</v>
       </c>
       <c r="U7" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1556,7 +1556,7 @@
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="AA7" t="n">
         <v>2.01</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.51</v>
+        <v>3.05</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="P10" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.05</v>
+        <v>2.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="U12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
         <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>3.95</v>
+        <v>3.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.87</v>
+        <v>6.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.85</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.65</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="R23" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC23" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
         <v>3.4</v>
@@ -4644,6 +4644,165 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
+        <v>46223.875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Central Norte</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Deportivo Morón</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3" t="n">
         <v>46223.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.93</v>
+        <v>1.24</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.14</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.28</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AF10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>2.93</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.95</v>
+        <v>3.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.87</v>
+        <v>6.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
         <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R13" t="n">
         <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AB13" t="n">
         <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="U14" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V19" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O23" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O8" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>2.4</v>
@@ -1703,34 +1703,34 @@
         <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF8" t="n">
         <v>1.72</v>
@@ -1752,7 +1752,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="U11" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>3.46</v>
+        <v>3.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2351,28 +2351,28 @@
         <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
         <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,61 +2633,61 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
         <v>1.5</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2795,61 +2795,61 @@
         <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="P15" t="n">
-        <v>4.43</v>
+        <v>5.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.56</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.07</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,77 +2954,77 @@
         <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>5.01</v>
+        <v>4.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.65</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.17</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>4.25</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.97</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.51</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.35</v>
       </c>
-      <c r="O22" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -899,10 +899,10 @@
         <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.76</v>
+        <v>2.52</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
@@ -929,7 +929,7 @@
         <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
         <v>1.21</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
         <v>1.57</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
         <v>1.4</v>
@@ -1379,7 +1379,7 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1391,7 +1391,7 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.28</v>
@@ -1400,16 +1400,16 @@
         <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB6" t="n">
         <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
@@ -1565,10 +1565,10 @@
         <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
         <v>1.05</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
         <v>2.27</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.87</v>
+        <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.2</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>2.93</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.08</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>3.13</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.93</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,61 +2156,61 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>5.87</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
         <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.54</v>
+        <v>2.34</v>
       </c>
       <c r="AG11" t="n">
         <v>1.5</v>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.27</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="U12" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.46</v>
+        <v>3.27</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2510,28 +2510,28 @@
         <v>1.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
         <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O15" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>5.01</v>
+        <v>3.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
         <v>1.36</v>
@@ -2840,13 +2840,13 @@
         <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
         <v>1.93</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
         <v>2.3</v>
@@ -2966,16 +2966,16 @@
         <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
@@ -2996,19 +2996,19 @@
         <v>1.98</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
         <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.05</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.2</v>
+        <v>1.81</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>3.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB18" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.56</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.42</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2.64</v>
+        <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4.85</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.65</v>
       </c>
-      <c r="O22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P22" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>3.17</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC22" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,65 +4064,65 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.1</v>
       </c>
-      <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.17</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>1.58</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>4.25</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.16</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.97</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -746,7 +746,7 @@
         <v>3.34</v>
       </c>
       <c r="U2" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
         <v>1.59</v>
@@ -782,7 +782,7 @@
         <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1064,28 +1064,28 @@
         <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
         <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
         <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC4" t="n">
         <v>2.97</v>
@@ -1094,7 +1094,7 @@
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF4" t="n">
         <v>1.74</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1214,13 +1214,13 @@
         <v>2.97</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="U5" t="n">
         <v>2.88</v>
@@ -1259,7 +1259,7 @@
         <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
         <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,47 +2189,47 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2324,19 +2324,19 @@
         <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
         <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
@@ -2345,34 +2345,34 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
         <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2480,49 +2480,49 @@
         <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>3.27</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
         <v>3.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
         <v>2.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
@@ -2531,7 +2531,7 @@
         <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.46</v>
+        <v>4.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
         <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
         <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
         <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
         <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AF16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.52</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.56</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.05</v>
       </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.58</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.64</v>
+        <v>2.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.22</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S22" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.83</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.21</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
         <v>2.68</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1364,10 +1364,10 @@
         <v>6.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1397,16 +1397,16 @@
         <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
         <v>1.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD6" t="n">
         <v>1.3</v>
@@ -2159,10 +2159,10 @@
         <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
         <v>3.14</v>
@@ -2177,10 +2177,10 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2192,7 +2192,7 @@
         <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
         <v>2.88</v>
@@ -2201,7 +2201,7 @@
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.08</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
         <v>1.5</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>4.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AA12" t="n">
         <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
@@ -2504,34 +2504,34 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -2663,34 +2663,34 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y14" t="n">
         <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.89</v>
+        <v>5.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>5.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q16" t="n">
         <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.13</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.2</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.42</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.58</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.22</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="P21" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3920,10 +3920,10 @@
         <v>1.83</v>
       </c>
       <c r="S22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
         <v>4</v>
@@ -3947,7 +3947,7 @@
         <v>2.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
         <v>5.65</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>4.85</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T23" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="V23" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -767,7 +767,7 @@
         <v>1.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC2" t="n">
         <v>2.19</v>
@@ -776,13 +776,13 @@
         <v>1.59</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
         <v>2.97</v>
@@ -1217,7 +1217,7 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
         <v>2.67</v>
@@ -1241,25 +1241,25 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>1.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.4</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.13</v>
-      </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>4.44</v>
+        <v>3.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
         <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,47 +2348,47 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
         <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB13" t="n">
         <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.18</v>
+        <v>4.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -2663,34 +2663,34 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
         <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>5.01</v>
+        <v>3.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="P16" t="n">
-        <v>3.65</v>
+        <v>5.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.22</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>3.04</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="P22" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,28 +4064,28 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P23" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>1.2</v>
@@ -4097,31 +4097,31 @@
         <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.35</v>
+        <v>5.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>4.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.06</v>
       </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4415,16 +4415,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -734,25 +734,25 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="S2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -761,28 +761,28 @@
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
         <v>3</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
         <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O5" t="n">
         <v>3.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="Q5" t="n">
         <v>2.97</v>
@@ -1232,7 +1232,7 @@
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
         <v>1.28</v>
@@ -1241,19 +1241,19 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
         <v>1.71</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1379,7 +1379,7 @@
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
@@ -1397,7 +1397,7 @@
         <v>1.28</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
         <v>1.8</v>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>6.4</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R7" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
         <v>1.39</v>
@@ -1562,7 +1562,7 @@
         <v>2.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>3.55</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>1.96</v>
       </c>
       <c r="O8" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.43</v>
+        <v>3.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.11</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.93</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.13</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.28</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>2.93</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.4</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2165,16 +2165,16 @@
         <v>3.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S11" t="n">
         <v>1.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U11" t="n">
         <v>4</v>
@@ -2192,7 +2192,7 @@
         <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AA11" t="n">
         <v>3.1</v>
@@ -2207,7 +2207,7 @@
         <v>1.05</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
         <v>2.6</v>
@@ -2229,7 +2229,7 @@
         <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2360,7 +2360,7 @@
         <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
         <v>1.08</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
         <v>1.22</v>
@@ -2504,34 +2504,34 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
         <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="P14" t="n">
-        <v>4.44</v>
+        <v>3.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -2669,28 +2669,28 @@
         <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.89</v>
+        <v>6.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.01</v>
+        <v>4.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,25 +3110,25 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="P17" t="n">
-        <v>3.16</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
         <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T17" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
         <v>2.63</v>
@@ -3149,10 +3149,10 @@
         <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
         <v>3.8</v>
@@ -3164,10 +3164,10 @@
         <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="P19" t="n">
         <v>2.6</v>
@@ -3440,7 +3440,7 @@
         <v>2.78</v>
       </c>
       <c r="R19" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
         <v>1.2</v>
@@ -3590,10 +3590,10 @@
         <v>2.87</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -3611,7 +3611,7 @@
         <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="W20" t="n">
         <v>1.22</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.35</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
         <v>3.3</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.83</v>
       </c>
-      <c r="S23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.21</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
         <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q24" t="n">
         <v>3.15</v>
@@ -4256,13 +4256,13 @@
         <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AB24" t="n">
         <v>1.3</v>
@@ -4280,7 +4280,7 @@
         <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,22 +734,22 @@
         <v>1.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
         <v>1.12</v>
@@ -761,28 +761,28 @@
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AC2" t="n">
         <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
         <v>1.04</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
         <v>3.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="Q5" t="n">
         <v>2.97</v>
@@ -1241,19 +1241,19 @@
         <v>3.08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
         <v>1.71</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.14</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.93</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.28</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AF10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>2.93</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB11" t="n">
         <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>6.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.89</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,28 +2633,28 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="O14" t="n">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
         <v>1.22</v>
@@ -2669,28 +2669,28 @@
         <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.16</v>
+        <v>5.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.08</v>
+        <v>2.87</v>
       </c>
       <c r="O19" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.87</v>
+        <v>2.08</v>
       </c>
       <c r="O20" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T20" t="n">
         <v>4.1</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.75</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V20" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.22</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,28 +3746,28 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>3.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S21" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V21" t="n">
         <v>1.2</v>
@@ -3779,31 +3779,31 @@
         <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.35</v>
       </c>
-      <c r="O23" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK23" t="n">
-        <v>2.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>4.85</v>
       </c>
       <c r="P24" t="n">
-        <v>3.27</v>
+        <v>5.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="S24" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>4.25</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.67</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.11</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.35</v>
+        <v>1.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.06</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>2.85</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,16 +4574,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4644,165 +4644,6 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46223.875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Central Norte</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Deportivo Morón</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" s="3" t="n">
         <v>46223.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
         <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
         <v>2.4</v>
@@ -1700,7 +1700,7 @@
         <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="V8" t="n">
         <v>1.4</v>
@@ -1718,7 +1718,7 @@
         <v>3.34</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
         <v>1.9</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.28</v>
       </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AF9" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>2.93</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.93</v>
+        <v>1.23</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
         <v>1.66</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,19 +2189,19 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="AD11" t="n">
         <v>1.08</v>
@@ -2210,10 +2210,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
         <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>5.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AB13" t="n">
         <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>6.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.89</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.37</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.64</v>
+        <v>2.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.08</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,28 +3746,28 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.27</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S21" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
         <v>1.2</v>
@@ -3779,31 +3779,31 @@
         <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.35</v>
+        <v>5.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK21" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>4.85</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.06</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>2.92</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,28 +4064,28 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>3.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V23" t="n">
         <v>1.2</v>
@@ -4097,31 +4097,31 @@
         <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>3.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>6.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="O24" t="n">
-        <v>4.85</v>
+        <v>3.05</v>
       </c>
       <c r="P24" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.06</v>
+        <v>1.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.92</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
         <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
         <v>2.66</v>
@@ -1559,13 +1559,13 @@
         <v>2.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
@@ -1574,10 +1574,10 @@
         <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
         <v>2.41</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>3.21</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.14</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.93</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>4.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.28</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.23</v>
+        <v>2.96</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,31 +2156,31 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -2189,31 +2189,31 @@
         <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
         <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.27</v>
+        <v>2.07</v>
       </c>
       <c r="AA12" t="n">
         <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.89</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.16</v>
+        <v>5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.07</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P15" t="n">
-        <v>3.9</v>
+        <v>4.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AK15" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.97</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.07</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="AF16" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.37</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.42</v>
+        <v>1.94</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.37</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.08</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.94</v>
+        <v>2.42</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.64</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>4.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.83</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.21</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>1.31</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.28</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>1.11</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.36</v>
+        <v>2.85</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.35</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.85</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>5.2</v>
+        <v>3.27</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>3.17</v>
       </c>
       <c r="R22" t="n">
-        <v>2.56</v>
+        <v>1.92</v>
       </c>
       <c r="S22" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T22" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>1.97</v>
+        <v>3.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.06</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>2.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.31</v>
+        <v>3.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.92</v>
+        <v>1.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,28 +4064,28 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.7</v>
       </c>
-      <c r="P23" t="n">
-        <v>3.27</v>
-      </c>
       <c r="Q23" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="S23" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>1.2</v>
@@ -4097,31 +4097,31 @@
         <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.35</v>
+        <v>5.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK23" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.51</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4219,47 +4219,47 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="AA24" t="n">
         <v>2.4</v>
@@ -4268,19 +4268,19 @@
         <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>2.62</v>
       </c>
       <c r="P25" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
         <v>2.68</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.85</v>
+        <v>6.5</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.5</v>
+        <v>7.95</v>
       </c>
       <c r="R2" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="AC2" t="n">
         <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="Q3" t="n">
         <v>2.8</v>
@@ -923,7 +923,7 @@
         <v>3</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.72</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="S4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>2.97</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1205,16 +1205,16 @@
         <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="Q5" t="n">
         <v>2.97</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
         <v>1.38</v>
@@ -1223,7 +1223,7 @@
         <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
@@ -1244,16 +1244,16 @@
         <v>1.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
         <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF5" t="n">
         <v>1.71</v>
@@ -1364,10 +1364,10 @@
         <v>6.25</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q6" t="n">
         <v>6</v>
@@ -1388,22 +1388,22 @@
         <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>2.97</v>
@@ -1415,10 +1415,10 @@
         <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>1.99</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
         <v>1.07</v>
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>3.48</v>
       </c>
       <c r="P7" t="n">
         <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="R7" t="n">
         <v>2.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="U7" t="n">
         <v>2.9</v>
@@ -1565,7 +1565,7 @@
         <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
@@ -1593,7 +1593,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.97</v>
+        <v>7.17</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.34</v>
+        <v>5.55</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.64</v>
+        <v>1.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.59</v>
+        <v>3.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.45</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>3.21</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.14</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.96</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>6.07</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
         <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,28 +2507,28 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
         <v>1.53</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.07</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P15" t="n">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.07</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.97</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,61 +2954,61 @@
         <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2.15</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.62</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.01</v>
+        <v>2.55</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>1.93</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>3.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>1.64</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T19" t="n">
         <v>4.1</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4.75</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.22</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>2.82</v>
       </c>
       <c r="O20" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="U20" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="V20" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.93</v>
+        <v>6.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AB20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE20" t="n">
+      <c r="AF20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.35</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,68 +3901,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="R22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S22" t="n">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R23" t="n">
         <v>2.7</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.83</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>1.94</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.83</v>
+        <v>1.32</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>2.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>1.86</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.36</v>
+        <v>2.57</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.49</v>
+        <v>1.69</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>3.48</v>
+        <v>3.94</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>5.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T7" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="U7" t="n">
         <v>2.9</v>
@@ -1562,7 +1562,7 @@
         <v>2.02</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
         <v>3.34</v>
@@ -1574,10 +1574,10 @@
         <v>1.05</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
         <v>2.27</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
         <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.07</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="P12" t="n">
-        <v>3.42</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
         <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.18</v>
+        <v>3.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.7</v>
+        <v>6.07</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="U14" t="n">
         <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB14" t="n">
         <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P17" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.1</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S18" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.07</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.74</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.55</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.64</v>
+        <v>2.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P19" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
         <v>2.78</v>
@@ -3446,10 +3446,10 @@
         <v>1.2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="V19" t="n">
         <v>1.67</v>
@@ -3461,7 +3461,7 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z19" t="n">
         <v>6.01</v>
@@ -3590,13 +3590,13 @@
         <v>2.82</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
         <v>2.55</v>
@@ -3626,10 +3626,10 @@
         <v>6.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AC20" t="n">
         <v>1.63</v>
@@ -3638,7 +3638,7 @@
         <v>1.93</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF20" t="n">
         <v>1.33</v>
@@ -3660,7 +3660,7 @@
         <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>3.27</v>
       </c>
       <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U21" t="n">
         <v>3.7</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4</v>
-      </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AK21" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.36</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,69 +3901,69 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.1</v>
       </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.83</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,84 +4219,84 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="P24" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.17</v>
+        <v>2.83</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S24" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="V24" t="n">
         <v>1.25</v>
       </c>
       <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.03</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK24" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="O25" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="P25" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>2.68</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>7.17</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.36</v>
+        <v>2.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.5</v>
+        <v>3.21</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.14</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.96</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>7.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.21</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.28</v>
       </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.07</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,31 +2315,31 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="U12" t="n">
         <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,31 +2348,31 @@
         <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
         <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="S13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.07</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
         <v>1.67</v>
       </c>
       <c r="T14" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,28 +2666,28 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
         <v>1.53</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,69 +3106,69 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.7</v>
       </c>
-      <c r="U17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.44</v>
       </c>
       <c r="P18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="R18" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.1</v>
       </c>
-      <c r="AC18" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>4.75</v>
       </c>
       <c r="P21" t="n">
-        <v>3.27</v>
+        <v>5.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="R21" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="S21" t="n">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="U21" t="n">
-        <v>3.7</v>
+        <v>1.94</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.57</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.11</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.1</v>
+        <v>1.32</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.3</v>
+        <v>2.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>6.4</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.5</v>
+        <v>2.47</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.53</v>
+        <v>2.57</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,68 +3901,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>2.83</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="S22" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.09</v>
+        <v>2.59</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE22" t="n">
         <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>4.75</v>
+        <v>2.71</v>
       </c>
       <c r="P23" t="n">
-        <v>5.4</v>
+        <v>3.27</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="S23" t="n">
-        <v>1.17</v>
+        <v>1.69</v>
       </c>
       <c r="T23" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.94</v>
+        <v>3.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
-        <v>7</v>
+        <v>2.11</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.32</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.86</v>
+        <v>6.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="O24" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.83</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE24" t="n">
         <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>7.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S9" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.89</v>
+        <v>1.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>2.96</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7.17</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.05</v>
+        <v>2.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>2.96</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.07</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>3.48</v>
+        <v>3.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>6.07</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,31 +2474,31 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,31 +2507,31 @@
         <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
         <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="S14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2666,31 +2666,31 @@
         <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
         <v>2.57</v>
@@ -3284,7 +3284,7 @@
         <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
         <v>2.7</v>
@@ -3293,7 +3293,7 @@
         <v>2.88</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
@@ -3302,13 +3302,13 @@
         <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
         <v>1.81</v>
@@ -3320,7 +3320,7 @@
         <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
         <v>1.62</v>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3742,68 +3742,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="P21" t="n">
-        <v>5.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4.4</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.84</v>
+        <v>1.14</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.47</v>
+        <v>1.71</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,68 +3901,68 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P22" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.83</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE22" t="n">
         <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="P24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.83</v>
-      </c>
       <c r="S24" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>1.94</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.09</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.83</v>
+        <v>1.32</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>2.47</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
         <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="Q3" t="n">
         <v>2.8</v>
@@ -905,7 +905,7 @@
         <v>2.59</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
         <v>1.36</v>
@@ -941,7 +941,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>4.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="R4" t="n">
         <v>2.02</v>
@@ -1061,37 +1061,37 @@
         <v>1.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.17</v>
+        <v>1.89</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE4" t="n">
         <v>1.03</v>
@@ -1100,7 +1100,7 @@
         <v>1.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U6" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
         <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AG6" t="n">
         <v>1.77</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
         <v>5.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
         <v>2.06</v>
       </c>
       <c r="S7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T7" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.04</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
         <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.51</v>
+        <v>3.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
         <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q10" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2.4</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.81</v>
-      </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.04</v>
+        <v>2.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.9</v>
+        <v>1.34</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="P11" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.16</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
         <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.07</v>
+        <v>6.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK12" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2470,29 +2470,29 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
@@ -2504,7 +2504,7 @@
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
         <v>1.61</v>
@@ -2516,13 +2516,13 @@
         <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
         <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK13" t="n">
         <v>1.52</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2642,10 +2642,10 @@
         <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
         <v>1.62</v>
@@ -2663,19 +2663,19 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
         <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
         <v>6.5</v>
@@ -2684,7 +2684,7 @@
         <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
         <v>2.6</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2954,61 +2954,61 @@
         <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,84 +3106,84 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="P17" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.57</v>
       </c>
       <c r="R17" t="n">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.99</v>
+        <v>2.88</v>
       </c>
       <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.72</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="R18" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.4</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3742,68 +3742,68 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="O21" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.83</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE21" t="n">
         <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3901,84 +3901,84 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S22" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.62</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.71</v>
+        <v>4.75</v>
       </c>
       <c r="P23" t="n">
-        <v>3.27</v>
+        <v>5.4</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB23" t="n">
         <v>3</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC23" t="n">
-        <v>6.4</v>
+        <v>1.86</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.53</v>
+        <v>2.88</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.87</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="T24" t="n">
-        <v>4.4</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>3.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>2.11</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.32</v>
+        <v>2.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.86</v>
+        <v>6.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.84</v>
+        <v>1.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.47</v>
+        <v>1.49</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="O25" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>7.57</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>5.55</v>
       </c>
       <c r="P2" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.95</v>
+        <v>8.5</v>
       </c>
       <c r="R2" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
@@ -752,31 +752,31 @@
         <v>1.62</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AD2" t="n">
         <v>1.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF2" t="n">
         <v>1.86</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>2.02</v>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
         <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="S5" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T5" t="n">
         <v>2.67</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
         <v>1.07</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>3.27</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
         <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
         <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.55</v>
+        <v>6.02</v>
       </c>
       <c r="AA9" t="n">
         <v>1.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
         <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="AK9" t="n">
         <v>1.11</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O10" t="n">
         <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.08</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.34</v>
+        <v>1.81</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2152,68 +2152,68 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="O11" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.16</v>
+        <v>5.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.73</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
         <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q12" t="n">
         <v>3.14</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,68 +2470,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="P13" t="n">
-        <v>3.18</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S13" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.7</v>
+        <v>6.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4.45</v>
+        <v>4.22</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R15" t="n">
         <v>2.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.32</v>
-      </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.1</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AF15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P16" t="n">
-        <v>4.22</v>
+        <v>4.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.57</v>
+        <v>2.15</v>
       </c>
       <c r="R17" t="n">
-        <v>2.07</v>
+        <v>2.65</v>
       </c>
       <c r="S17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.4</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.5</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="R19" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="T19" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U19" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="V19" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.01</v>
+        <v>6.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.22</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="O20" t="n">
-        <v>4.15</v>
+        <v>3.64</v>
       </c>
       <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.87</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.5</v>
+        <v>6.09</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>3.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S21" t="n">
         <v>1.65</v>
@@ -3788,13 +3788,13 @@
         <v>2.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
         <v>7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE21" t="n">
         <v>1.03</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="P22" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4226,77 +4226,77 @@
         <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.62</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.27</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>3.27</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z9" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>3.04</v>
+        <v>1.53</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>2.82</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>6.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>3.04</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2152,56 +2152,56 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.75</v>
       </c>
-      <c r="P11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.7</v>
+        <v>6.15</v>
       </c>
       <c r="AD11" t="n">
         <v>1.07</v>
@@ -2210,10 +2210,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2311,23 +2311,23 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
         <v>1.64</v>
@@ -2336,43 +2336,43 @@
         <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>1.36</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,35 +2470,35 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O13" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="P13" t="n">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.85</v>
       </c>
       <c r="S13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
@@ -2507,10 +2507,10 @@
         <v>1.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AA13" t="n">
         <v>3.1</v>
@@ -2519,19 +2519,19 @@
         <v>1.34</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,68 +2629,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P15" t="n">
-        <v>4.22</v>
+        <v>4.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>4.45</v>
+        <v>4.22</v>
       </c>
       <c r="Q16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R16" t="n">
         <v>2.2</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.32</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.1</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AF16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R17" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.5</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U18" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3742,11 +3742,11 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="O21" t="n">
         <v>2.8</v>
@@ -3791,7 +3791,7 @@
         <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="AD21" t="n">
         <v>1.11</v>
@@ -3911,7 +3911,7 @@
         <v>2.53</v>
       </c>
       <c r="P22" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
         <v>3.15</v>
@@ -3932,7 +3932,7 @@
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
         <v>1.15</v>
@@ -3941,10 +3941,10 @@
         <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
         <v>1.3</v>
@@ -3959,10 +3959,10 @@
         <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>1.95</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T24" t="n">
         <v>2.36</v>
@@ -4253,7 +4253,7 @@
         <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
         <v>1.46</v>
@@ -4265,13 +4265,13 @@
         <v>2.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>4.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE24" t="n">
         <v>1.01</v>
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>3.27</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.82</v>
+        <v>2.31</v>
       </c>
       <c r="V8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.81</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.27</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>2.31</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>6.02</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.53</v>
+        <v>3.04</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.68</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.02</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>3.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S11" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="V11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2311,56 +2311,56 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.75</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S12" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.7</v>
+        <v>6.15</v>
       </c>
       <c r="AD12" t="n">
         <v>1.07</v>
@@ -2369,10 +2369,10 @@
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>3.94</v>
+        <v>3.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
         <v>4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,68 +2629,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O14" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4.45</v>
+        <v>4.22</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R15" t="n">
         <v>2.2</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.32</v>
-      </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.1</v>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AF15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P16" t="n">
-        <v>4.22</v>
+        <v>4.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>1.63</v>
       </c>
       <c r="O17" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U17" t="n">
-        <v>2.88</v>
+        <v>1.99</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.14</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.29</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.5</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4.75</v>
+        <v>3.04</v>
       </c>
       <c r="P23" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="S23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.18</v>
       </c>
-      <c r="T23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="AE23" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.88</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.04</v>
+        <v>4.75</v>
       </c>
       <c r="P24" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="S24" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>4.4</v>
       </c>
       <c r="U24" t="n">
-        <v>3.38</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="W24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.01</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.06</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.47</v>
+        <v>6.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.56</v>
+        <v>3</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.66</v>
+        <v>1.86</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>2.88</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>7.57</v>
+        <v>8.5</v>
       </c>
       <c r="O2" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="S2" t="n">
         <v>1.22</v>
@@ -746,10 +746,10 @@
         <v>3.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W2" t="n">
         <v>1.14</v>
@@ -758,31 +758,31 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB2" t="n">
         <v>2.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
         <v>1.06</v>
@@ -890,25 +890,25 @@
         <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.16</v>
+        <v>3.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
         <v>2.05</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -920,7 +920,7 @@
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
         <v>2.09</v>
@@ -929,7 +929,7 @@
         <v>1.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
         <v>1.21</v>
@@ -941,7 +941,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
         <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="U4" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="V4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.33</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1211,10 +1211,10 @@
         <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
         <v>1.43</v>
@@ -1229,16 +1229,16 @@
         <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="AA5" t="n">
         <v>2.13</v>
@@ -1247,10 +1247,10 @@
         <v>1.69</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE5" t="n">
         <v>1.07</v>
@@ -1259,7 +1259,7 @@
         <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,61 +1361,61 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S6" t="n">
         <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
         <v>1.77</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>2.58</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,31 +1520,31 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>5.93</v>
+        <v>4.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
@@ -1553,19 +1553,19 @@
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AD7" t="n">
         <v>1.25</v>
@@ -1574,10 +1574,10 @@
         <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="R8" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q9" t="n">
         <v>7</v>
       </c>
-      <c r="O9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6.5</v>
-      </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.02</v>
+        <v>5.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
         <v>1.64</v>
@@ -2177,43 +2177,43 @@
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.36</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE11" t="n">
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2311,35 +2311,35 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="P12" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
         <v>1.85</v>
       </c>
       <c r="S12" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2348,10 +2348,10 @@
         <v>1.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AA12" t="n">
         <v>3.1</v>
@@ -2360,19 +2360,19 @@
         <v>1.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.15</v>
+        <v>6.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2477,13 +2477,13 @@
         <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.73</v>
@@ -2495,7 +2495,7 @@
         <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V13" t="n">
         <v>1.2</v>
@@ -2513,16 +2513,16 @@
         <v>2.13</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
         <v>5.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE13" t="n">
         <v>1.03</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,68 +2629,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2798,46 +2798,46 @@
         <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>4.22</v>
+        <v>4.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="R15" t="n">
         <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
         <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
         <v>1.26</v>
@@ -2846,10 +2846,10 @@
         <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,61 +2951,61 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="P16" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R16" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V16" t="n">
         <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
         <v>2</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="S17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.5</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.95</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.88</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z18" t="n">
-        <v>3.14</v>
+        <v>6.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>1.31</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.82</v>
+        <v>2.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.08</v>
+        <v>1.32</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P19" t="n">
         <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T19" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X19" t="n">
         <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB19" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,16 +3587,16 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
         <v>3.64</v>
       </c>
       <c r="P20" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R20" t="n">
         <v>2.45</v>
@@ -3605,10 +3605,10 @@
         <v>1.2</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U20" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="V20" t="n">
         <v>1.67</v>
@@ -3617,25 +3617,25 @@
         <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
         <v>1.12</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.09</v>
+        <v>4</v>
       </c>
       <c r="AA20" t="n">
         <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="n">
         <v>1.26</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3752,7 +3752,7 @@
         <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q21" t="n">
         <v>3.8</v>
@@ -3791,7 +3791,7 @@
         <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.65</v>
+        <v>6.62</v>
       </c>
       <c r="AD21" t="n">
         <v>1.11</v>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="O22" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
         <v>3.4</v>
@@ -3917,7 +3917,7 @@
         <v>3.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
         <v>1.62</v>
@@ -3926,7 +3926,7 @@
         <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
@@ -3941,10 +3941,10 @@
         <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AB22" t="n">
         <v>1.3</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="O23" t="n">
-        <v>3.04</v>
+        <v>4.6</v>
       </c>
       <c r="P23" t="n">
-        <v>3.42</v>
+        <v>5.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="S23" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="U23" t="n">
-        <v>3.38</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="W23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.01</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.47</v>
+        <v>5.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.56</v>
+        <v>2.87</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.66</v>
+        <v>1.89</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>2.85</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>5.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.85</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="S24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.18</v>
       </c>
-      <c r="T24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X24" t="n">
+      <c r="AE24" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.88</v>
+        <v>1.6</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="O25" t="n">
         <v>2.75</v>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU27"/>
+  <dimension ref="A1:AU26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,41 +631,41 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>8.85</v>
+        <v>8.5</v>
       </c>
       <c r="O2">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P2">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>6.93</v>
+        <v>7.2</v>
       </c>
       <c r="R2">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S2">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T2">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.12</v>
@@ -674,25 +674,25 @@
         <v>4.75</v>
       </c>
       <c r="AA2">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB2">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC2">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK2">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,42 +787,42 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="O3">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>3.14</v>
+        <v>3.43</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="R3">
         <v>2.05</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
         <v>3</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -834,16 +834,16 @@
         <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA3">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB3">
         <v>1.72</v>
       </c>
       <c r="AC3">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD3">
         <v>1.21</v>
@@ -859,46 +859,46 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>["57", "62", "65"]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,130 +938,130 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="S4">
+        <v>1.45</v>
+      </c>
+      <c r="T4">
+        <v>2.44</v>
+      </c>
+      <c r="U4">
+        <v>3.08</v>
+      </c>
+      <c r="V4">
+        <v>1.35</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
         <v>1.33</v>
       </c>
-      <c r="T4">
-        <v>2.88</v>
-      </c>
-      <c r="U4">
-        <v>2.75</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
-      <c r="W4">
-        <v>1.1</v>
-      </c>
-      <c r="X4">
-        <v>1</v>
-      </c>
-      <c r="Y4">
-        <v>1.23</v>
-      </c>
       <c r="Z4">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="AA4">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AB4">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC4">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
+        <v>1.09</v>
+      </c>
+      <c r="AF4">
+        <v>2.08</v>
+      </c>
+      <c r="AG4">
+        <v>1.67</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["11", "34", "43", "50", "70"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>["52"]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.08</v>
       </c>
-      <c r="AF4">
-        <v>1.74</v>
-      </c>
-      <c r="AG4">
-        <v>1.94</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.22</v>
-      </c>
       <c r="AK4">
+        <v>2.03</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>6</v>
+      </c>
+      <c r="AN4">
         <v>2</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
-      <c r="AN4">
-        <v>-1</v>
-      </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,79 +1113,79 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O5">
         <v>3.1</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
+        <v>1.01</v>
+      </c>
+      <c r="X5">
         <v>1.02</v>
       </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z5">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA5">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="AB5">
         <v>1.7</v>
       </c>
       <c r="AC5">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AG5">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "90+3"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1197,34 +1197,34 @@
         <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1439,106 +1439,106 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="O7">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P7">
-        <v>6.4</v>
+        <v>4.95</v>
       </c>
       <c r="Q7">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="R7">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="V7">
+        <v>1.33</v>
+      </c>
+      <c r="W7">
+        <v>1.03</v>
+      </c>
+      <c r="X7">
+        <v>1.03</v>
+      </c>
+      <c r="Y7">
         <v>1.36</v>
       </c>
-      <c r="W7">
-        <v>1.04</v>
-      </c>
-      <c r="X7">
-        <v>1.02</v>
-      </c>
-      <c r="Y7">
-        <v>1.3</v>
-      </c>
       <c r="Z7">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="AA7">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
         <v>1.76</v>
       </c>
       <c r="AC7">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AG7">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>["80"]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,24 +1602,24 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
         <v>1.96</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q8">
         <v>2.4</v>
@@ -1634,86 +1634,86 @@
         <v>3</v>
       </c>
       <c r="U8">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="V8">
         <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA8">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC8">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "64", "90+4"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ8">
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,42 +1753,42 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
         <v>2.5</v>
       </c>
       <c r="O9">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q9">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
         <v>1.28</v>
@@ -1797,86 +1797,86 @@
         <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
+        <v>1.13</v>
+      </c>
+      <c r="Z9">
+        <v>4.55</v>
+      </c>
+      <c r="AA9">
+        <v>1.62</v>
+      </c>
+      <c r="AB9">
+        <v>2.29</v>
+      </c>
+      <c r="AC9">
+        <v>2.55</v>
+      </c>
+      <c r="AD9">
+        <v>1.46</v>
+      </c>
+      <c r="AE9">
         <v>1.15</v>
       </c>
-      <c r="Z9">
-        <v>4.33</v>
-      </c>
-      <c r="AA9">
-        <v>1.64</v>
-      </c>
-      <c r="AB9">
-        <v>2.21</v>
-      </c>
-      <c r="AC9">
-        <v>2.43</v>
-      </c>
-      <c r="AD9">
-        <v>1.49</v>
-      </c>
-      <c r="AE9">
-        <v>1.19</v>
-      </c>
       <c r="AF9">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "33"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "64"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
         <v>6</v>
       </c>
       <c r="O10">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="Q10">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U10">
         <v>2.05</v>
       </c>
       <c r="V10">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="Z10">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AA10">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AB10">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AC10">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD10">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE10">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF10">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,37 +2009,37 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="AK10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2098,23 +2098,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="O11">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="P11">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="Q11">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
         <v>1.62</v>
@@ -2132,19 +2132,19 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y11">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z11">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AA11">
         <v>3.1</v>
       </c>
       <c r="AB11">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AC11">
         <v>6.5</v>
@@ -2175,7 +2175,7 @@
         <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
@@ -2271,7 +2271,7 @@
         <v>2.62</v>
       </c>
       <c r="P12">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="Q12">
         <v>3.14</v>
@@ -2298,7 +2298,7 @@
         <v>1.14</v>
       </c>
       <c r="Y12">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z12">
         <v>2.38</v>
@@ -2307,13 +2307,13 @@
         <v>2.88</v>
       </c>
       <c r="AB12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC12">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AD12">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE12">
         <v>1.03</v>
@@ -2322,7 +2322,7 @@
         <v>2.28</v>
       </c>
       <c r="AG12">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
         <v>1.5</v>
@@ -2424,47 +2424,47 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="O13">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="P13">
-        <v>3.27</v>
+        <v>3.45</v>
       </c>
       <c r="Q13">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R13">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S13">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U13">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="V13">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W13">
         <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y13">
         <v>1.61</v>
       </c>
       <c r="Z13">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AA13">
         <v>2.81</v>
@@ -2473,10 +2473,10 @@
         <v>1.33</v>
       </c>
       <c r="AC13">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AD13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE13">
         <v>1.03</v>
@@ -2485,7 +2485,7 @@
         <v>2.38</v>
       </c>
       <c r="AG13">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK13">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2587,29 +2587,29 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="P14">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S14">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="T14">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="U14">
         <v>3.75</v>
@@ -2621,31 +2621,31 @@
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y14">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z14">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AA14">
         <v>3.1</v>
       </c>
       <c r="AB14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC14">
-        <v>5.89</v>
+        <v>6.15</v>
       </c>
       <c r="AD14">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE14">
         <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AG14">
         <v>1.5</v>
@@ -2664,7 +2664,7 @@
         <v>1.35</v>
       </c>
       <c r="AK14">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,28 +2757,28 @@
         <v>1.75</v>
       </c>
       <c r="O15">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>5.01</v>
+        <v>4.95</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="R15">
         <v>2.2</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T15">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2787,31 +2787,31 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA15">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
         <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
         <v>1.8</v>
       </c>
       <c r="AG15">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O17">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>4.4</v>
+        <v>3.89</v>
       </c>
       <c r="Q17">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R17">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S17">
         <v>1.22</v>
@@ -3104,7 +3104,7 @@
         <v>1.95</v>
       </c>
       <c r="V17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W17">
         <v>1.16</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6.55</v>
       </c>
       <c r="AA17">
         <v>1.31</v>
       </c>
       <c r="AB17">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AC17">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AD17">
         <v>1.83</v>
       </c>
       <c r="AE17">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF17">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AG17">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK17">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="Q18">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S18">
         <v>1.36</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="U18">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
         <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>3.08</v>
+        <v>3.38</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC18">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE18">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
         <v>1.68</v>
       </c>
       <c r="AG18">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q19">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
+        <v>1.17</v>
+      </c>
+      <c r="T19">
+        <v>4.2</v>
+      </c>
+      <c r="U19">
+        <v>1.95</v>
+      </c>
+      <c r="V19">
+        <v>1.82</v>
+      </c>
+      <c r="W19">
         <v>1.2</v>
       </c>
-      <c r="T19">
-        <v>4.1</v>
-      </c>
-      <c r="U19">
-        <v>1.97</v>
-      </c>
-      <c r="V19">
-        <v>1.67</v>
-      </c>
-      <c r="W19">
-        <v>1.16</v>
-      </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>5.93</v>
+        <v>6.1</v>
       </c>
       <c r="AA19">
         <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="AC19">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AD19">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AE19">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P20">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="R20">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="U20">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="V20">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z20">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AC20">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AD20">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AE20">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG20">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="O21">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P21">
-        <v>5.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q21">
+        <v>1.73</v>
+      </c>
+      <c r="R21">
+        <v>2.65</v>
+      </c>
+      <c r="S21">
+        <v>1.16</v>
+      </c>
+      <c r="T21">
+        <v>4.6</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21">
         <v>1.79</v>
       </c>
-      <c r="R21">
-        <v>2.56</v>
-      </c>
-      <c r="S21">
-        <v>1.17</v>
-      </c>
-      <c r="T21">
-        <v>4.4</v>
-      </c>
-      <c r="U21">
-        <v>1.97</v>
-      </c>
-      <c r="V21">
-        <v>1.83</v>
-      </c>
       <c r="W21">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>7.5</v>
+        <v>5.85</v>
       </c>
       <c r="AA21">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AC21">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD21">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE21">
         <v>1.33</v>
       </c>
       <c r="AF21">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK21">
         <v>2.85</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,69 +3891,69 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>2.61</v>
       </c>
       <c r="O22">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P22">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z22">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AA22">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="AB22">
+        <v>1.33</v>
+      </c>
+      <c r="AC22">
+        <v>6.62</v>
+      </c>
+      <c r="AD22">
+        <v>1.11</v>
+      </c>
+      <c r="AE22">
+        <v>1.03</v>
+      </c>
+      <c r="AF22">
+        <v>2.28</v>
+      </c>
+      <c r="AG22">
         <v>1.53</v>
       </c>
-      <c r="AC22">
-        <v>0</v>
-      </c>
-      <c r="AD22">
-        <v>0</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0</v>
-      </c>
-      <c r="AG22">
-        <v>0</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G23">
@@ -4054,84 +4054,84 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="O23">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="R23">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="S23">
         <v>1.62</v>
       </c>
       <c r="T23">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="U23">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V23">
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z23">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AA23">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AB23">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC23">
-        <v>5.65</v>
+        <v>6.4</v>
       </c>
       <c r="AD23">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG23">
+        <v>1.57</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>1.36</v>
+      </c>
+      <c r="AK23">
         <v>1.53</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.35</v>
-      </c>
-      <c r="AK23">
-        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,68 +4217,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O24">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="Q24">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="T24">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="U24">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="V24">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X24">
         <v>1.1</v>
       </c>
       <c r="Y24">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="Z24">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AA24">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB24">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AC24">
-        <v>6.4</v>
+        <v>4.66</v>
       </c>
       <c r="AD24">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AE24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG24">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4417,16 +4417,16 @@
         <v>0</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="O26">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="P26">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="Z26">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA26">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AB26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4650,169 +4650,6 @@
         <v>0</v>
       </c>
       <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-07-20 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Central Norte</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Deportivo Morón</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>2.87</v>
-      </c>
-      <c r="O27">
-        <v>2.68</v>
-      </c>
-      <c r="P27">
-        <v>2.5</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>1.71</v>
-      </c>
-      <c r="Z27">
-        <v>2</v>
-      </c>
-      <c r="AA27">
-        <v>3.4</v>
-      </c>
-      <c r="AB27">
-        <v>1.33</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
         <is>
           <t>2026-07-20 21:30:00</t>
         </is>

--- a/jogos_2026-07-20.xlsx
+++ b/jogos_2026-07-20.xlsx
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2743,14 +2743,14 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "49"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.61</v>
+        <v>2.26</v>
       </c>
       <c r="O22">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P22">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="Q22">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="R22">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="S22">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="T22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U22">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="V22">
         <v>1.2</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z22">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AA22">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AB22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC22">
-        <v>6.62</v>
+        <v>6.4</v>
       </c>
       <c r="AD22">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AE22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="AG22">
+        <v>1.57</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.36</v>
+      </c>
+      <c r="AK22">
         <v>1.53</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.35</v>
-      </c>
-      <c r="AK22">
-        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.26</v>
+        <v>2.61</v>
       </c>
       <c r="O23">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="Q23">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="R23">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="S23">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T23">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U23">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V23">
         <v>1.2</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Y23">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z23">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AA23">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AB23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC23">
-        <v>6.4</v>
+        <v>6.62</v>
       </c>
       <c r="AD23">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AG23">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
